--- a/reports/OYPB_브랜드별_시딩_비용_광고성과_최신화.xlsx
+++ b/reports/OYPB_브랜드별_시딩_비용_광고성과_최신화.xlsx
@@ -391,32 +391,32 @@
     <xf numFmtId="165" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -817,7 +817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:N22"/>
+  <dimension ref="B2:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
     <col width="8.796875" customWidth="1" style="3" min="1" max="1"/>
@@ -853,7 +853,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>※ 통계 : 25.04 ~ 26.09 기준으로 글로벌 시딩 167건이 포함되어 있습니다.</t>
+          <t>※ 통계 : 25.04 ~ 26.09 기준 · 국내외 전체 2,139건(글로벌 167건 = JP 99 + US 68) · 26.09.07 갱신</t>
         </is>
       </c>
       <c r="C3" s="2" t="n"/>
@@ -872,7 +872,7 @@
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>※ RD : 국내외 전체 2,139건 기준(단 성과는 조회수 집계분 2,050건 기준)으로 작성되었습니다.</t>
+          <t>※ RD : 수량·비용은 2,139건 기준, 조회수·참여수는 성과 집계분 2,086건 기준(IMD 2,050 + 바이오힐보 US 36)</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -997,7 +997,7 @@
       </c>
       <c r="N7" s="40" t="n"/>
     </row>
-    <row r="8" ht="26.4" customHeight="1" s="35">
+    <row r="8" ht="39.6" customHeight="1" s="35">
       <c r="B8" s="13" t="inlineStr">
         <is>
           <t>아이디얼포맨</t>
@@ -1062,7 +1062,7 @@
         <f>SUM(C9:D9)</f>
         <v/>
       </c>
-      <c r="F9" s="43" t="n">
+      <c r="F9" s="41" t="n">
         <v>15535558</v>
       </c>
       <c r="G9" s="41">
@@ -1078,540 +1078,636 @@
       <c r="J9" s="41" t="n">
         <v>1337</v>
       </c>
-      <c r="K9" s="43" t="n">
+      <c r="K9" s="41" t="n">
         <v>124304394</v>
       </c>
-      <c r="L9" s="43" t="n">
+      <c r="L9" s="41" t="n">
         <v>729266288</v>
       </c>
-      <c r="M9" s="18">
+      <c r="M9" s="15">
         <f>L9/K9</f>
         <v/>
       </c>
-      <c r="N9" s="19" t="inlineStr">
+      <c r="N9" s="16" t="inlineStr">
         <is>
           <t>11개 브랜드 전체 퍼포먼스 광고비 중 44% 집행 → UGC&amp;협력광고 중심 티트리 라인 스케일업 필요</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="20" t="inlineStr">
+    <row r="10" ht="26.4" customHeight="1" s="35">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>라운드어라운드</t>
         </is>
       </c>
-      <c r="C10" s="44" t="n">
+      <c r="C10" s="41" t="n">
         <v>281</v>
       </c>
-      <c r="D10" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="44">
+      <c r="D10" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="41">
         <f>SUM(C10:D10)</f>
         <v/>
       </c>
-      <c r="F10" s="44" t="n">
+      <c r="F10" s="41" t="n">
         <v>2413068</v>
       </c>
-      <c r="G10" s="44">
+      <c r="G10" s="41">
         <f>F10/E10</f>
         <v/>
       </c>
-      <c r="H10" s="44" t="n">
+      <c r="H10" s="41" t="n">
         <v>41731</v>
       </c>
-      <c r="I10" s="45" t="n">
+      <c r="I10" s="42" t="n">
         <v>25.51</v>
       </c>
-      <c r="J10" s="44" t="n">
+      <c r="J10" s="41" t="n">
         <v>1475</v>
       </c>
-      <c r="K10" s="44" t="n">
+      <c r="K10" s="41" t="n">
         <v>133848</v>
       </c>
-      <c r="L10" s="44" t="n">
+      <c r="L10" s="41" t="n">
         <v>348140</v>
       </c>
-      <c r="M10" s="22">
+      <c r="M10" s="15">
         <f>L10/K10</f>
         <v/>
       </c>
-      <c r="N10" s="23" t="inlineStr">
+      <c r="N10" s="16" t="inlineStr">
         <is>
           <t>PR키트 진행 등 참여율 1위</t>
         </is>
       </c>
     </row>
     <row r="11" ht="39.6" customHeight="1" s="35">
-      <c r="B11" s="24" t="inlineStr">
-        <is>
-          <t>바이오힐보</t>
-        </is>
-      </c>
-      <c r="C11" s="46" t="n">
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>바이오힐보 (국내)</t>
+        </is>
+      </c>
+      <c r="C11" s="41" t="n">
         <v>195</v>
       </c>
-      <c r="D11" s="47" t="n">
-        <v>75</v>
-      </c>
-      <c r="E11" s="46">
+      <c r="D11" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="41">
         <f>SUM(C11:D11)</f>
         <v/>
       </c>
-      <c r="F11" s="46" t="n">
-        <v>5484319</v>
-      </c>
-      <c r="G11" s="46">
+      <c r="F11" s="41" t="n">
+        <v>5440064</v>
+      </c>
+      <c r="G11" s="41">
         <f>F11/E11</f>
         <v/>
       </c>
-      <c r="H11" s="46" t="n">
-        <v>24951</v>
-      </c>
-      <c r="I11" s="48" t="n">
-        <v>7.21</v>
-      </c>
-      <c r="J11" s="46" t="n">
-        <v>1586</v>
-      </c>
-      <c r="K11" s="46" t="n">
+      <c r="H11" s="41" t="n">
+        <v>24922</v>
+      </c>
+      <c r="I11" s="42" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="J11" s="41" t="n">
+        <v>1521</v>
+      </c>
+      <c r="K11" s="41" t="n">
         <v>56333229</v>
       </c>
-      <c r="L11" s="46" t="n">
+      <c r="L11" s="41" t="n">
         <v>172219558</v>
       </c>
-      <c r="M11" s="27">
+      <c r="M11" s="15">
         <f>L11/K11</f>
         <v/>
       </c>
-      <c r="N11" s="28" t="inlineStr">
-        <is>
-          <t>평균조회수·파트너십 광고 성과 개선 여지 존재
-(글로벌 75건은 25.8~9월 빅빙세일 나노 시딩 테스트)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26.4" customHeight="1" s="35">
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t>퍼포먼스 광고 성과는 전량 국내에서 발생
+최대 조회수 764,503뷰</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="39.6" customHeight="1" s="35">
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>식물나라</t>
+          <t>바이오힐보 (해외·JP)</t>
         </is>
       </c>
       <c r="C12" s="41" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="D12" s="41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E12" s="41">
         <f>SUM(C12:D12)</f>
         <v/>
       </c>
       <c r="F12" s="41" t="n">
-        <v>2788821</v>
+        <v>44255</v>
       </c>
       <c r="G12" s="41">
         <f>F12/E12</f>
         <v/>
       </c>
       <c r="H12" s="41" t="n">
+        <v>29</v>
+      </c>
+      <c r="I12" s="42" t="n">
+        <v>37.64</v>
+      </c>
+      <c r="J12" s="41" t="n">
+        <v>57447</v>
+      </c>
+      <c r="K12" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>25.8~9월 빅빙세일 나노 시딩 테스트
+조회수·참여 모두 저조</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="39.6" customHeight="1" s="35">
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>바이오힐보 (해외·US)</t>
+        </is>
+      </c>
+      <c r="C13" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="41" t="n">
+        <v>68</v>
+      </c>
+      <c r="E13" s="41">
+        <f>SUM(C13:D13)</f>
+        <v/>
+      </c>
+      <c r="F13" s="41" t="n">
+        <v>4739117</v>
+      </c>
+      <c r="G13" s="41">
+        <f>F13/E13</f>
+        <v/>
+      </c>
+      <c r="H13" s="41" t="n">
+        <v>24134</v>
+      </c>
+      <c r="I13" s="42" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="J13" s="41" t="n">
+        <v>1243</v>
+      </c>
+      <c r="K13" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <t>68건 중 36건 성과 확보 · 건당 131,642뷰(국내의 4.7배)
+최대 2,954,129뷰 = 전체 1위 / CPV는 청구 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="39.6" customHeight="1" s="35">
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>식물나라</t>
+        </is>
+      </c>
+      <c r="C14" s="41" t="n">
+        <v>140</v>
+      </c>
+      <c r="D14" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="41">
+        <f>SUM(C14:D14)</f>
+        <v/>
+      </c>
+      <c r="F14" s="41" t="n">
+        <v>2788821</v>
+      </c>
+      <c r="G14" s="41">
+        <f>F14/E14</f>
+        <v/>
+      </c>
+      <c r="H14" s="41" t="n">
         <v>20319</v>
       </c>
-      <c r="I12" s="42" t="n">
+      <c r="I14" s="42" t="n">
         <v>11.65</v>
       </c>
-      <c r="J12" s="41" t="n">
+      <c r="J14" s="41" t="n">
         <v>1599</v>
       </c>
-      <c r="K12" s="41" t="n">
+      <c r="K14" s="41" t="n">
         <v>14985030</v>
       </c>
-      <c r="L12" s="41" t="n">
+      <c r="L14" s="41" t="n">
         <v>118255596</v>
       </c>
-      <c r="M12" s="15">
-        <f>L12/K12</f>
-        <v/>
-      </c>
-      <c r="N12" s="16" t="inlineStr">
+      <c r="M14" s="43">
+        <f>L14/K14</f>
+        <v/>
+      </c>
+      <c r="N14" s="16" t="inlineStr">
         <is>
           <t>빅&amp;스몰웨이브의 시작(25.05)
 마이크로 IMC 성과 가장 잘 워킹하는 브랜드</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="26.4" customHeight="1" s="35">
-      <c r="B13" s="13" t="inlineStr">
+    <row r="15" ht="39.6" customHeight="1" s="35">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>웨이크메이크</t>
         </is>
       </c>
-      <c r="C13" s="43" t="n">
+      <c r="C15" s="41" t="n">
         <v>70</v>
       </c>
-      <c r="D13" s="41" t="n">
+      <c r="D15" s="41" t="n">
         <v>60</v>
       </c>
-      <c r="E13" s="41">
-        <f>SUM(C13:D13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="41" t="n">
+      <c r="E15" s="41">
+        <f>SUM(C15:D15)</f>
+        <v/>
+      </c>
+      <c r="F15" s="41" t="n">
         <v>3143931</v>
       </c>
-      <c r="G13" s="41">
-        <f>F13/E13</f>
-        <v/>
-      </c>
-      <c r="H13" s="41" t="n">
+      <c r="G15" s="41">
+        <f>F15/E15</f>
+        <v/>
+      </c>
+      <c r="H15" s="41" t="n">
         <v>18097</v>
       </c>
-      <c r="I13" s="42" t="n">
+      <c r="I15" s="42" t="n">
         <v>12.36</v>
       </c>
-      <c r="J13" s="41" t="n">
+      <c r="J15" s="41" t="n">
         <v>2147</v>
       </c>
-      <c r="K13" s="41" t="n">
+      <c r="K15" s="41" t="n">
         <v>16409851</v>
       </c>
-      <c r="L13" s="41" t="n">
+      <c r="L15" s="41" t="n">
         <v>113788050</v>
       </c>
-      <c r="M13" s="18">
-        <f>L13/K13</f>
-        <v/>
-      </c>
-      <c r="N13" s="19" t="inlineStr">
+      <c r="M15" s="15">
+        <f>L15/K15</f>
+        <v/>
+      </c>
+      <c r="N15" s="16" t="inlineStr">
         <is>
           <t>26.04 행사 및 올영픽 등 미존재로
 UGC 협업 수량 증대해도 좋을 것으로 판단</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="26.4" customHeight="1" s="35">
-      <c r="B14" s="20" t="inlineStr">
+    <row r="16" ht="39.6" customHeight="1" s="35">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>루테카</t>
         </is>
       </c>
-      <c r="C14" s="44" t="n">
+      <c r="C16" s="41" t="n">
         <v>124</v>
       </c>
-      <c r="D14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="44">
-        <f>SUM(C14:D14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="44" t="n">
+      <c r="D16" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="41">
+        <f>SUM(C16:D16)</f>
+        <v/>
+      </c>
+      <c r="F16" s="41" t="n">
         <v>1655285</v>
       </c>
-      <c r="G14" s="44">
-        <f>F14/E14</f>
-        <v/>
-      </c>
-      <c r="H14" s="44" t="n">
+      <c r="G16" s="41">
+        <f>F16/E16</f>
+        <v/>
+      </c>
+      <c r="H16" s="41" t="n">
         <v>9444</v>
       </c>
-      <c r="I14" s="45" t="n">
+      <c r="I16" s="42" t="n">
         <v>13.59</v>
       </c>
-      <c r="J14" s="44" t="n">
+      <c r="J16" s="41" t="n">
         <v>2382</v>
       </c>
-      <c r="K14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="29" t="inlineStr">
+      <c r="K16" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N14" s="23" t="inlineStr">
+      <c r="N16" s="16" t="inlineStr">
         <is>
           <t>퍼포먼스 광고 미집행
 (브랜드 fade out)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="26.4" customHeight="1" s="35">
-      <c r="B15" s="13" t="inlineStr">
+    <row r="17" ht="39.6" customHeight="1" s="35">
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>컬러그램</t>
         </is>
       </c>
-      <c r="C15" s="43" t="n">
+      <c r="C17" s="41" t="n">
         <v>45</v>
       </c>
-      <c r="D15" s="41" t="n">
+      <c r="D17" s="41" t="n">
         <v>32</v>
       </c>
-      <c r="E15" s="49">
-        <f>SUM(C15:D15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="41" t="n">
+      <c r="E17" s="41">
+        <f>SUM(C17:D17)</f>
+        <v/>
+      </c>
+      <c r="F17" s="41" t="n">
         <v>1583237</v>
       </c>
-      <c r="G15" s="41">
-        <f>F15/E15</f>
-        <v/>
-      </c>
-      <c r="H15" s="41" t="n">
+      <c r="G17" s="41">
+        <f>F17/E17</f>
+        <v/>
+      </c>
+      <c r="H17" s="41" t="n">
         <v>8511</v>
       </c>
-      <c r="I15" s="42" t="n">
+      <c r="I17" s="42" t="n">
         <v>20.49</v>
       </c>
-      <c r="J15" s="41" t="n">
+      <c r="J17" s="41" t="n">
         <v>3812</v>
       </c>
-      <c r="K15" s="41" t="n">
+      <c r="K17" s="41" t="n">
         <v>7670607</v>
       </c>
-      <c r="L15" s="41" t="n">
+      <c r="L17" s="41" t="n">
         <v>61405809</v>
       </c>
-      <c r="M15" s="15">
-        <f>L15/K15</f>
-        <v/>
-      </c>
-      <c r="N15" s="19" t="inlineStr">
+      <c r="M17" s="15">
+        <f>L17/K17</f>
+        <v/>
+      </c>
+      <c r="N17" s="16" t="inlineStr">
         <is>
           <t>전체 브랜드 중 ROAS 2위(800% 이상)
 → 협업 수량 증가 필요</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="26.4" customHeight="1" s="35">
-      <c r="B16" s="20" t="inlineStr">
+    <row r="18" ht="39.6" customHeight="1" s="35">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>케어플러스</t>
         </is>
       </c>
-      <c r="C16" s="44" t="n">
+      <c r="C18" s="41" t="n">
         <v>32</v>
       </c>
-      <c r="D16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="44">
-        <f>SUM(C16:D16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="44" t="n">
+      <c r="D18" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="41">
+        <f>SUM(C18:D18)</f>
+        <v/>
+      </c>
+      <c r="F18" s="41" t="n">
         <v>188488</v>
       </c>
-      <c r="G16" s="44">
-        <f>F16/E16</f>
-        <v/>
-      </c>
-      <c r="H16" s="44" t="n">
+      <c r="G18" s="41">
+        <f>F18/E18</f>
+        <v/>
+      </c>
+      <c r="H18" s="41" t="n">
         <v>1839</v>
       </c>
-      <c r="I16" s="45" t="inlineStr">
+      <c r="I18" s="42" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="J18" s="41" t="n">
+        <v>2012</v>
+      </c>
+      <c r="K18" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J16" s="44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N16" s="23" t="inlineStr">
-        <is>
-          <t>26.07 UGC 첫 협업
-퍼포먼스 광고 미집행</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26.4" customHeight="1" s="35">
-      <c r="B17" s="13" t="inlineStr">
+      <c r="N18" s="16" t="inlineStr">
+        <is>
+          <t>26.07 UGC 첫 협업 · 퍼포먼스 광고 미집행
+원고료 마이크로 5건×20만 + 나노 27건×10만</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="39.6" customHeight="1" s="35">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>필리밀리</t>
         </is>
       </c>
-      <c r="C17" s="41" t="n">
+      <c r="C19" s="41" t="n">
         <v>27</v>
       </c>
-      <c r="D17" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="41">
-        <f>SUM(C17:D17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="41" t="n">
+      <c r="D19" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="41">
+        <f>SUM(C19:D19)</f>
+        <v/>
+      </c>
+      <c r="F19" s="41" t="n">
         <v>1353401</v>
       </c>
-      <c r="G17" s="41">
-        <f>F17/E17</f>
-        <v/>
-      </c>
-      <c r="H17" s="41" t="n">
+      <c r="G19" s="41">
+        <f>F19/E19</f>
+        <v/>
+      </c>
+      <c r="H19" s="41" t="n">
         <v>1967</v>
       </c>
-      <c r="I17" s="42" t="n">
+      <c r="I19" s="42" t="n">
         <v>4.65</v>
       </c>
-      <c r="J17" s="41" t="n">
+      <c r="J19" s="41" t="n">
         <v>3203</v>
       </c>
-      <c r="K17" s="41" t="n">
+      <c r="K19" s="41" t="n">
         <v>14086284</v>
       </c>
-      <c r="L17" s="41" t="n">
+      <c r="L19" s="41" t="n">
         <v>121998372</v>
       </c>
-      <c r="M17" s="18">
-        <f>L17/K17</f>
-        <v/>
-      </c>
-      <c r="N17" s="19" t="inlineStr">
+      <c r="M19" s="15">
+        <f>L19/K19</f>
+        <v/>
+      </c>
+      <c r="N19" s="44" t="inlineStr">
         <is>
           <t>전체 브랜드 중 ROAS 1위
 최저 CPA 확보</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="20" t="inlineStr">
+    <row r="20" ht="26.4" customHeight="1" s="35">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>올더베러</t>
         </is>
       </c>
-      <c r="C18" s="44" t="n">
+      <c r="C20" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="D18" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="44">
-        <f>SUM(C18:D18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="44" t="n">
+      <c r="D20" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="45">
+        <f>SUM(C20:D20)</f>
+        <v/>
+      </c>
+      <c r="F20" s="45" t="n">
         <v>396952</v>
       </c>
-      <c r="G18" s="44">
-        <f>F18/E18</f>
-        <v/>
-      </c>
-      <c r="H18" s="44" t="n">
+      <c r="G20" s="45">
+        <f>F20/E20</f>
+        <v/>
+      </c>
+      <c r="H20" s="45" t="n">
         <v>3440</v>
       </c>
-      <c r="I18" s="45" t="n">
+      <c r="I20" s="46" t="n">
         <v>5.04</v>
       </c>
-      <c r="J18" s="44" t="n">
+      <c r="J20" s="45" t="n">
         <v>581</v>
       </c>
-      <c r="K18" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="29" t="inlineStr">
+      <c r="K20" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N18" s="23" t="inlineStr">
+      <c r="N20" s="16" t="inlineStr">
         <is>
           <t>퍼포먼스 광고 미집행</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="31" t="inlineStr">
+    <row r="21" ht="26.4" customHeight="1" s="35">
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>소계</t>
         </is>
       </c>
-      <c r="C19" s="50">
-        <f>SUM(C8:C18)</f>
-        <v/>
-      </c>
-      <c r="D19" s="50">
-        <f>SUM(D8:D18)</f>
-        <v/>
-      </c>
-      <c r="E19" s="50">
-        <f>SUM(E8:E18)</f>
-        <v/>
-      </c>
-      <c r="F19" s="50">
-        <f>SUM(F8:F18)</f>
-        <v/>
-      </c>
-      <c r="G19" s="50">
-        <f>F19/E19</f>
-        <v/>
-      </c>
-      <c r="H19" s="50">
-        <f>SUM(H8:H18)</f>
-        <v/>
-      </c>
-      <c r="I19" s="51" t="n">
-        <v>9.42</v>
-      </c>
-      <c r="J19" s="50" t="n">
-        <v>1334</v>
-      </c>
-      <c r="K19" s="50">
-        <f>SUM(K8:K18)</f>
-        <v/>
-      </c>
-      <c r="L19" s="50">
-        <f>SUM(L8:L18)</f>
-        <v/>
-      </c>
-      <c r="M19" s="33">
-        <f>L19/K19</f>
-        <v/>
-      </c>
-      <c r="N19" s="34" t="inlineStr">
+      <c r="C21" s="48">
+        <f>SUM(C8:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="48">
+        <f>SUM(D8:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="48">
+        <f>SUM(E8:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="48">
+        <f>SUM(F8:F20)</f>
+        <v/>
+      </c>
+      <c r="G21" s="48">
+        <f>F21/E21</f>
+        <v/>
+      </c>
+      <c r="H21" s="48">
+        <f>SUM(H8:H20)</f>
+        <v/>
+      </c>
+      <c r="I21" s="49" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="J21" s="48" t="n">
+        <v>1345</v>
+      </c>
+      <c r="K21" s="48">
+        <f>SUM(K8:K20)</f>
+        <v/>
+      </c>
+      <c r="L21" s="48">
+        <f>SUM(L8:L20)</f>
+        <v/>
+      </c>
+      <c r="M21" s="50">
+        <f>L21/K21</f>
+        <v/>
+      </c>
+      <c r="N21" s="51" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>※ 참여수 = 좋아요 + 댓글 / 평균 CPV = 크리에이터 원고료 ÷ 조회수 / 평균 CPE = 크리에이터 원고료 ÷ 참여수</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>※ 원고료 기준 : 크리에이터 원고료 총 488,708,205원(마크업·VAT 제외, 조회수 집계분 2,050건 기준). 청구 기준 세금계산서 총액 931,288,075원과는 별개 지표입니다.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>※ 케어플러스는 원고료 데이터 미기재(IMD 공란)로 CPV·CPE 산출 불가 → "-" 표기.</t>
+          <t>※ 참여수 = 좋아요 + 댓글 / 평균 CPV = 크리에이터 원고료 ÷ 조회수 / 평균 CPE = 크리에이터 원고료 ÷ 참여수</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>※ 소계 CPV·CPE는 원고료가 확정된 2,050건 기준(원고료 492,408,205원 ÷ 조회수 51,873,648 / 참여 366,236). 바이오힐보 US는 원고료 미기재로 청구액 30,000,000원 기준이라 소계에서 제외했다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>※ 세금계산서 발행 확정 총액 930,344,264원(26.02~08 확정 840,514,264 + 25년 발행 89,830,000). 위 표의 원고료는 마크업·VAT 제외 금액으로 청구액과 다른 지표다.</t>
         </is>
       </c>
     </row>

--- a/reports/OYPB_브랜드별_시딩_비용_광고성과_최신화.xlsx
+++ b/reports/OYPB_브랜드별_시딩_비용_광고성과_최신화.xlsx
@@ -1707,7 +1707,7 @@
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>※ 세금계산서 발행 확정 총액 930,344,264원(26.02~08 확정 840,514,264 + 25년 발행 89,830,000). 위 표의 원고료는 마크업·VAT 제외 금액으로 청구액과 다른 지표다.</t>
+          <t>※ 세금계산서 발행 확정 총액 840,514,264원(26.02~08 발행분이 전부 · 2025 진행분 정산·바이오힐보 US 포함). 위 표의 원고료는 마크업·VAT 제외 금액으로 청구액과 다른 지표다.</t>
         </is>
       </c>
     </row>

--- a/reports/OYPB_브랜드별_시딩_비용_광고성과_최신화.xlsx
+++ b/reports/OYPB_브랜드별_시딩_비용_광고성과_최신화.xlsx
@@ -1707,7 +1707,7 @@
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>※ 세금계산서 발행 확정 총액 840,514,264원(26.02~08 발행분이 전부 · 2025 진행분 정산·바이오힐보 US 포함). 위 표의 원고료는 마크업·VAT 제외 금액으로 청구액과 다른 지표다.</t>
+          <t>※ 세금계산서 발행 확정 총액 900,344,264원(26.02~08 확정 840,514,264 + 25년 발행 59,830,000 · 바이오힐보 US 30,000,000 포함). 위 표의 원고료는 마크업·VAT 제외 금액으로 청구액과 다른 지표다.</t>
         </is>
       </c>
     </row>
